--- a/Firmalar.xlsx
+++ b/Firmalar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muratfirar\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728CD94B-C6B6-48F7-9267-11510D600FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DAF539-A859-4641-8D16-560A8E6DE9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{6725CD23-C56C-4265-8992-94566BDA1AEC}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{6725CD23-C56C-4265-8992-94566BDA1AEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>firma_unvan</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>ozel_negatifler</t>
+  </si>
+  <si>
+    <t>SÜPER FİLM AMBALAJ</t>
+  </si>
+  <si>
+    <t>SANKO GRUBU</t>
+  </si>
+  <si>
+    <t>KOLİN İNŞAAT TURİZM</t>
   </si>
 </sst>
 </file>
@@ -438,11 +447,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9C6441-56C2-45A4-BC68-C128EAB4107D}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -494,6 +503,25 @@
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
